--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_20/return_vol/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_20/return_vol/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,16 +462,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.08791116709867786</v>
+        <v>-0.01695242521271445</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2634645952107391</v>
+        <v>0.1641760939297111</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.435984855484305</v>
+        <v>-0.1266411040143267</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.6409045170141665</v>
+        <v>-0.1771876828900574</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.1760105558842076</v>
+        <v>0.1560218733295081</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.5675654952712995</v>
+        <v>-0.1226480564226428</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>62.43877651975344</v>
+        <v>35.98271122036039</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.3640239250374412</v>
+        <v>-0.1307763997604932</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2387401601444948</v>
+        <v>0.284101150585516</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.915255669959551</v>
+        <v>-0.4246985159011765</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-2.424947561479743</v>
+        <v>-0.6048875183152324</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3859722320501369</v>
+        <v>0.2351192487877058</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.973664788678038</v>
+        <v>-0.5775621528648729</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>62.88452221575074</v>
+        <v>42.52361333401509</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.1667068472898978</v>
+        <v>-0.0789359141022532</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2005559613145502</v>
+        <v>0.2256532954466368</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.9210164801660762</v>
+        <v>-0.3327030634616262</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-1.297385525568073</v>
+        <v>-0.45424651823652</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2575272523375967</v>
+        <v>0.2264349209721669</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.6716294746942326</v>
+        <v>-0.3624006085875446</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>66.99603479220983</v>
+        <v>68.86209996059249</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.1808184611625652</v>
+        <v>0.05721130083804726</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2368141207163776</v>
+        <v>0.3349885327738181</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-0.8232415549852919</v>
+        <v>0.2941827010493578</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-1.255618983864947</v>
+        <v>0.4403234944779845</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2518015898353974</v>
+        <v>0.1760656471765684</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.7448014067812264</v>
+        <v>0.338763261110598</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>74.92216603553121</v>
+        <v>77.37508358308894</v>
       </c>
     </row>
     <row r="6">
@@ -636,29 +636,57 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.1134216774822805</v>
+        <v>-0.07527739749321083</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2316673676165738</v>
+        <v>0.2577327169551568</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.5330045786144672</v>
+        <v>-0.2423531191929199</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.7278311560675664</v>
+        <v>-0.3147750861685046</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1689262723744654</v>
+        <v>0.2609346044894567</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.6977068039548258</v>
+        <v>-0.2987487722824134</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>70.5951017041194</v>
+        <v>84.95942746130659</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026年截至07-31</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.450037127412461</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.3828020663328174</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1.912899684681929</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>2.97540587233379</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.1241022815881881</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>7.747056012809612</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>63.75327610027513</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>